--- a/Capitulo999_INSTITUTO/Taller2_2025/Proyecto2doCuatrimestreTaller2/Proyectos_Taller2_Anio2025.xlsx
+++ b/Capitulo999_INSTITUTO/Taller2_2025/Proyecto2doCuatrimestreTaller2/Proyectos_Taller2_Anio2025.xlsx
@@ -1098,11 +1098,11 @@
     <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2360,13 +2360,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
     </row>
     <row r="2" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B2" s="15" t="s">
@@ -2412,7 +2412,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="3" spans="2:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B3">
         <v>1</v>
       </c>
@@ -2450,7 +2450,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="4" spans="2:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B4">
         <v>2</v>
       </c>
@@ -2491,7 +2491,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="5" spans="2:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>3</v>
       </c>
@@ -2526,7 +2526,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="6" spans="2:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>4</v>
       </c>
@@ -2567,7 +2567,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="7" spans="2:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>5</v>
       </c>
@@ -2602,7 +2602,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:15" hidden="1" x14ac:dyDescent="0.2">
       <c r="B8">
         <v>6</v>
       </c>
@@ -2637,7 +2637,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="9" spans="2:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B9">
         <v>7</v>
       </c>
@@ -2675,7 +2675,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="10" spans="2:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B10">
         <v>9</v>
       </c>
@@ -2710,7 +2710,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="11" spans="2:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B11">
         <v>10</v>
       </c>
@@ -2748,7 +2748,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="12" spans="2:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B12">
         <v>11</v>
       </c>
@@ -2783,7 +2783,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="13" spans="2:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B13">
         <v>12</v>
       </c>
@@ -2821,7 +2821,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="14" spans="2:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B14">
         <v>13</v>
       </c>
@@ -2853,7 +2853,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="15" spans="2:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B15">
         <v>14</v>
       </c>
@@ -2894,7 +2894,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="16" spans="2:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B16">
         <v>15</v>
       </c>
@@ -2929,7 +2929,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="17" spans="2:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B17">
         <v>16</v>
       </c>
@@ -2964,7 +2964,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:15" hidden="1" x14ac:dyDescent="0.2">
       <c r="B18">
         <v>17</v>
       </c>
@@ -2996,7 +2996,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="19" spans="2:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B19">
         <v>18</v>
       </c>
@@ -3031,7 +3031,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:15" hidden="1" x14ac:dyDescent="0.2">
       <c r="B20">
         <v>19</v>
       </c>
@@ -3062,11 +3062,11 @@
       <c r="N20" t="s">
         <v>214</v>
       </c>
-      <c r="O20" s="28" t="s">
+      <c r="O20" s="27" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="21" spans="2:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B21">
         <v>20</v>
       </c>
@@ -3101,7 +3101,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="22" spans="2:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B22">
         <v>21</v>
       </c>
@@ -3136,7 +3136,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="23" spans="2:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B23">
         <v>22</v>
       </c>
@@ -3174,7 +3174,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="24" spans="2:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B24">
         <v>23</v>
       </c>
@@ -3209,7 +3209,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:15" hidden="1" x14ac:dyDescent="0.2">
       <c r="B25">
         <v>24</v>
       </c>
@@ -3241,7 +3241,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:15" hidden="1" x14ac:dyDescent="0.2">
       <c r="B26">
         <v>25</v>
       </c>
@@ -3276,7 +3276,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="27" spans="2:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B27">
         <v>26</v>
       </c>
@@ -3308,7 +3308,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:15" hidden="1" x14ac:dyDescent="0.2">
       <c r="B28">
         <v>27</v>
       </c>
@@ -3336,11 +3336,11 @@
       <c r="L28" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="O28" s="29" t="s">
+      <c r="O28" s="28" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="29" spans="2:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B29">
         <v>28</v>
       </c>
@@ -3354,7 +3354,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:15" hidden="1" x14ac:dyDescent="0.2">
       <c r="B30">
         <v>29</v>
       </c>
@@ -3377,7 +3377,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="31" spans="2:15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B31">
         <v>30</v>
       </c>
@@ -3400,12 +3400,8 @@
   </sheetData>
   <autoFilter ref="B2:O31">
     <filterColumn colId="13">
-      <filters blank="1">
-        <filter val="FALTA GRAFICO - CANTIDAD DE JUEGOS POR DESARROLLADOR"/>
-        <filter val="FALTA MOSTRAR PROYECTO FINAL"/>
-        <filter val="FALTA TERMINAR EL PROYECTO"/>
-        <filter val="FALTAN GRAFICOS"/>
-        <filter val="FALTAN GRAFICOS - RESOLVER QUERY EN EL MOTOR"/>
+      <filters>
+        <filter val="FINALIZADO"/>
       </filters>
     </filterColumn>
   </autoFilter>
